--- a/Heuristic_Evaluation.xlsx
+++ b/Heuristic_Evaluation.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,8 +103,27 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF7F3F00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF595959"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +175,16 @@
         <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -169,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -288,6 +317,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1005,7 +1094,7 @@
       </c>
       <c r="B28" s="36" t="inlineStr">
         <is>
-          <t>Fixed: 6  |  Partial: 1  |  Open: 46</t>
+          <t>Fixed: 6  |  Partial: 1  |  Open: 46  (of 53 findings)</t>
         </is>
       </c>
     </row>
@@ -1190,40 +1279,40 @@
       </c>
     </row>
     <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>H1-01</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F2" s="46" t="inlineStr">
         <is>
           <t>The Status readout cell transitions through Ready → Listening → Analysing → Ready, giving clear real-time feedback during the full analysis cycle.</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" s="19" t="inlineStr">
+      <c r="H2" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -1233,43 +1322,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J2" s="39" t="inlineStr"/>
+      <c r="J2" s="47" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>H1-02</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>Settings – Emotion Model card</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="46" t="inlineStr">
         <is>
           <t>The model status panel polls every 3 seconds and shows Idle / Loading / Ready / Error states with a spinner during download.</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -1279,41 +1368,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J3" s="39" t="inlineStr"/>
+      <c r="J3" s="47" t="inlineStr"/>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>H1-03</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n">
+      <c r="B4" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – Save button</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>After saving, the button shows "SAVED" for only 1.2 seconds before re-enabling. The feedback window is very short and easy to miss for users who look away.</t>
         </is>
       </c>
-      <c r="G4" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="G4" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="50" t="inlineStr">
         <is>
           <t>Extend feedback to 3 seconds; consider a persistent toast notification.</t>
         </is>
@@ -1323,41 +1412,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr"/>
+      <c r="J4" s="47" t="inlineStr"/>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>H1-04</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – canvas</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>The canvas has a small static label and f/k parameter readout, but no indication the simulation is actively running vs. frozen. A first-time user cannot tell whether the animation is live.</t>
         </is>
       </c>
-      <c r="G5" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="G5" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="50" t="inlineStr">
         <is>
           <t>Add a subtle animated pulse or LIVE badge to confirm the simulation is running.</t>
         </is>
@@ -1367,41 +1456,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J5" s="39" t="inlineStr"/>
+      <c r="J5" s="47" t="inlineStr"/>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>H1-05</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Home page – theme cards</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>Theme thumbnails are static images. There is no preview of what the theme looks like in motion; users cannot assess the dynamic nature of each artwork before selecting.</t>
         </is>
       </c>
-      <c r="G6" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="G6" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="50" t="inlineStr">
         <is>
           <t>Add short looping GIF or video previews on hover.</t>
         </is>
@@ -1411,41 +1500,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J6" s="39" t="inlineStr"/>
+      <c r="J6" s="47" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>H1-06</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>Visibility of System Status</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Gallery page</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>No progress indicator when deleting or favouriting items; the page reloads or the button state changes silently.</t>
         </is>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="50" t="inlineStr">
         <is>
           <t>Add a brief loading state to delete and favourite buttons.</t>
         </is>
@@ -1455,41 +1544,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J7" s="39" t="inlineStr"/>
+      <c r="J7" s="47" t="inlineStr"/>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>H2-01</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="B8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Match Between System and Real World</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Home page – theme descriptions</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>Theme names like "Anamorphic Resonance" and "Gray-Scott Reaction-Diffusion" are scientific/technical terms unfamiliar to general users.</t>
         </is>
       </c>
-      <c r="G8" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="G8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="50" t="inlineStr">
         <is>
           <t>Provide plain-English sub-descriptions alongside technical names.</t>
         </is>
@@ -1499,41 +1588,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J8" s="39" t="inlineStr"/>
+      <c r="J8" s="47" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>H2-02</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="B9" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>Match Between System and Real World</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – parameter readout</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>The f/k parameter values (e.g. "f = 0.0550  k = 0.0620") are chemistry simulation constants meaningless to non-specialist users.</t>
         </is>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="50" t="inlineStr">
         <is>
           <t>Replace with an emotion label or hide the readout entirely.</t>
         </is>
@@ -1543,43 +1632,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr"/>
+      <c r="J9" s="47" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>H2-03</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="B10" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>Match Between System and Real World</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>All visualization pages – mic button</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="46" t="inlineStr">
         <is>
           <t>The button label START LISTENING / END LISTENING is clear and consistent with common voice interface conventions.</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -1589,41 +1678,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr"/>
+      <c r="J10" s="47" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>H2-04</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="B11" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="48" t="inlineStr">
         <is>
           <t>Match Between System and Real World</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Settings page – Filename Pattern</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>The template syntax MY [PAGE_NAME] ART [NUMBER] uses square-bracket placeholders that are not explained. Users may not understand these are substitution variables.</t>
         </is>
       </c>
-      <c r="G11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="G11" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="50" t="inlineStr">
         <is>
           <t>Add a live preview of the resolved filename, or a tooltip explaining the tokens.</t>
         </is>
@@ -1633,41 +1722,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr"/>
+      <c r="J11" s="47" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>H2-05</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="B12" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
         <is>
           <t>Match Between System and Real World</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>Gallery page – card metadata</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>Cards show "Saved from bubbles" (route slug) rather than the display name. Uses internal identifiers in user-facing copy.</t>
         </is>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="50" t="inlineStr">
         <is>
           <t>Map route slugs to friendly display names in the gallery metadata.</t>
         </is>
@@ -1677,41 +1766,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J12" s="39" t="inlineStr"/>
+      <c r="J12" s="47" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>H3-01</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="48" t="inlineStr">
         <is>
           <t>User Control and Freedom</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – mic input</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>Once speech recognition starts, there is no way to cancel without clicking END LISTENING and waiting for the full analysis cycle. There is no discard option.</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="28" t="inlineStr">
+      <c r="H13" s="50" t="inlineStr">
         <is>
           <t>Add a Discard or Cancel action that stops the mic and clears the transcript without triggering analysis.</t>
         </is>
@@ -1721,41 +1810,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J13" s="39" t="inlineStr"/>
+      <c r="J13" s="47" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>H3-02</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="48" t="inlineStr">
         <is>
           <t>User Control and Freedom</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>Gallery – delete action</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>The delete action uses a browser confirm() dialog but there is no undo. Deletion is permanent and irreversible.</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="50" t="inlineStr">
         <is>
           <t>Implement a short-lived undo toast (5 seconds) after deletion, or a trash system.</t>
         </is>
@@ -1765,89 +1854,89 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr"/>
+      <c r="J14" s="47" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>H3-03</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="51" t="inlineStr">
         <is>
           <t>User Control and Freedom</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="51" t="inlineStr">
         <is>
           <t>Settings – Clear Gallery</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr">
         <is>
           <t>Clear Gallery deletes all artwork permanently with only a browser confirm(). No undo, no export prompt, no recovery.</t>
         </is>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="31" t="inlineStr">
+      <c r="H15" s="53" t="inlineStr">
         <is>
           <t>Require a typed confirmation (e.g. type DELETE) and offer a Download all first option before clearing.</t>
         </is>
       </c>
-      <c r="I15" s="40" t="inlineStr">
+      <c r="I15" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J15" s="41" t="inlineStr">
+      <c r="J15" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>H3-04</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>User Control and Freedom</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – theme switching</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>To switch themes users must return to the home page via the sidebar, abandoning the current session and losing analysis state.</t>
         </is>
       </c>
-      <c r="G16" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="G16" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="50" t="inlineStr">
         <is>
           <t>Add a theme-switcher dropdown or breadcrumb in the page header.</t>
         </is>
@@ -1857,41 +1946,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J16" s="39" t="inlineStr"/>
+      <c r="J16" s="47" t="inlineStr"/>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>H3-05</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="48" t="inlineStr">
         <is>
           <t>User Control and Freedom</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – canvas reset</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>There is no button to reset the Gray-Scott simulation without refreshing the page. If the pattern converges to an uninteresting state, users are stuck.</t>
         </is>
       </c>
-      <c r="G17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="G17" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="50" t="inlineStr">
         <is>
           <t>Add a Reset button that reinitialises both textures and re-injects default seeds.</t>
         </is>
@@ -1901,43 +1990,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J17" s="39" t="inlineStr"/>
+      <c r="J17" s="47" t="inlineStr"/>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>H4-01</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="44" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="46" t="inlineStr">
         <is>
           <t>All five visualization pages share the same control dock layout (mic button, text input, generate, status, emotion scores, transcript, save). Excellent platform-wide consistency.</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -1947,41 +2036,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J18" s="39" t="inlineStr"/>
+      <c r="J18" s="47" t="inlineStr"/>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>H4-02</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
+      <c r="B19" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="48" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Home page vs. visualization pages</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>The home page uses a different visual language (grid of cards) compared to the app-shell layout on all other pages. The sidebar is absent, creating a layout discontinuity.</t>
         </is>
       </c>
-      <c r="G19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="G19" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="50" t="inlineStr">
         <is>
           <t>Apply the full app-shell to the home page so the sidebar is always visible.</t>
         </is>
@@ -1991,41 +2080,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J19" s="39" t="inlineStr"/>
+      <c r="J19" s="47" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>H4-03</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="48" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Gallery vs. Favourites page</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>The Favourites page has no empty-state action button, unlike the Gallery page which links back to themes.</t>
         </is>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="50" t="inlineStr">
         <is>
           <t>Add a Browse Themes call-to-action in the Favourites empty state.</t>
         </is>
@@ -2035,41 +2124,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J20" s="39" t="inlineStr"/>
+      <c r="J20" s="47" t="inlineStr"/>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>H4-04</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Settings page – button placement</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>Save Changes and Restore to Default buttons are at the bottom of a long scrolling page with no sticky save bar, inconsistent with common settings patterns.</t>
         </is>
       </c>
-      <c r="G21" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="G21" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="50" t="inlineStr">
         <is>
           <t>Make the save/restore footer sticky or add a duplicate save button at the top.</t>
         </is>
@@ -2079,41 +2168,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J21" s="39" t="inlineStr"/>
+      <c r="J21" s="47" t="inlineStr"/>
     </row>
     <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>H4-05</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="48" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Sidebar – active state</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>Active page highlighting is set via Jinja2 template variables. If a developer forgets to set the flag in a new page, the active state will be missing.</t>
         </is>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="50" t="inlineStr">
         <is>
           <t>Drive active state from the current URL in JavaScript rather than template flags.</t>
         </is>
@@ -2123,41 +2212,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J22" s="39" t="inlineStr"/>
+      <c r="J22" s="47" t="inlineStr"/>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>H4-06</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="48" t="inlineStr">
         <is>
           <t>Consistency and Standards</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Gallery View page</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>The fullscreen view lacks the Rename and Favourite actions available on the gallery grid, creating an inconsistent feature set between views.</t>
         </is>
       </c>
-      <c r="G23" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="G23" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="50" t="inlineStr">
         <is>
           <t>Expose Rename and Favourite toggle on the gallery_view page.</t>
         </is>
@@ -2167,41 +2256,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J23" s="39" t="inlineStr"/>
+      <c r="J23" s="47" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>H5-01</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="48" t="inlineStr">
         <is>
           <t>Error Prevention</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – Generate button</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F24" s="50" t="inlineStr">
         <is>
           <t>Submitting an empty text field is silently ignored with no feedback. Users may click Generate and receive no response.</t>
         </is>
       </c>
-      <c r="G24" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="G24" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="50" t="inlineStr">
         <is>
           <t>Disable the Generate button when empty, or show an inline message.</t>
         </is>
@@ -2211,137 +2300,137 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J24" s="39" t="inlineStr"/>
+      <c r="J24" s="47" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>H5-02</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="51" t="inlineStr">
         <is>
           <t>Error Prevention</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="51" t="inlineStr">
         <is>
           <t>Settings – Clear Gallery</t>
         </is>
       </c>
-      <c r="E25" s="30" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F25" s="31" t="inlineStr">
+      <c r="E25" s="52" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F25" s="53" t="inlineStr">
         <is>
           <t>A single browser confirm() dialog is the only barrier before all gallery data is permanently deleted.</t>
         </is>
       </c>
-      <c r="G25" s="30" t="n">
+      <c r="G25" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="31" t="inlineStr">
+      <c r="H25" s="53" t="inlineStr">
         <is>
           <t>Require the user to type DELETE or tick a checkbox to confirm intent.</t>
         </is>
       </c>
-      <c r="I25" s="40" t="inlineStr">
+      <c r="I25" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J25" s="41" t="inlineStr">
+      <c r="J25" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>H5-03</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="55" t="inlineStr">
         <is>
           <t>Error Prevention</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="55" t="inlineStr">
         <is>
           <t>Settings – filename pattern</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="E26" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F26" s="57" t="inlineStr">
         <is>
           <t>No validation for the filename pattern input. Users could enter characters invalid in filenames causing silent save failures.</t>
         </is>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="57" t="inlineStr">
         <is>
           <t>Validate the pattern in real time, showing an error if illegal characters are entered.</t>
         </is>
       </c>
-      <c r="I26" s="40" t="inlineStr">
+      <c r="I26" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J26" s="41" t="inlineStr">
+      <c r="J26" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>H5-04</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="48" t="inlineStr">
         <is>
           <t>Error Prevention</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Bubbles page</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>If the WebGL fallback also fails, the canvas remains black with no user-facing error message.</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="G27" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="50" t="inlineStr">
         <is>
           <t>Add a visible error banner if the simulation cannot render after fallback attempts.</t>
         </is>
@@ -2351,91 +2440,91 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J27" s="39" t="inlineStr"/>
+      <c r="J27" s="47" t="inlineStr"/>
     </row>
     <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>H5-05</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="55" t="inlineStr">
         <is>
           <t>Error Prevention</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – mic button</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="E28" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F28" s="57" t="inlineStr">
         <is>
           <t>If microphone permission is denied, clicking START LISTENING shows "Mic error" but does not explain how to grant permission.</t>
         </is>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="57" t="inlineStr">
         <is>
           <t>Detect permission denied errors and show guidance linking to browser mic settings.</t>
         </is>
       </c>
-      <c r="I28" s="40" t="inlineStr">
+      <c r="I28" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J28" s="41" t="inlineStr">
+      <c r="J28" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>H6-01</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Recognition Rather Than Recall</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>Gallery page – artwork cards</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F29" s="46" t="inlineStr">
         <is>
           <t>Each saved artwork card shows the page it was created on and a thumbnail. Users can visually recognise their work without remembering filenames.</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="G29" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H29" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -2445,43 +2534,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J29" s="39" t="inlineStr"/>
+      <c r="J29" s="47" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>H6-02</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="44" t="inlineStr">
         <is>
           <t>Recognition Rather Than Recall</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>Settings page</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="46" t="inlineStr">
         <is>
           <t>All settings use dropdowns and checkboxes — users select from displayed options rather than recalling values.</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="G30" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H30" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -2491,41 +2580,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J30" s="39" t="inlineStr"/>
+      <c r="J30" s="47" t="inlineStr"/>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>H6-03</t>
         </is>
       </c>
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="48" t="inlineStr">
         <is>
           <t>Recognition Rather Than Recall</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – emotion scores</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
         <is>
           <t>The emotion scores panel only appears after analysis. Before a first analysis, users see "Waiting for input..." with no example of what the output will look like.</t>
         </is>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="25" t="inlineStr">
+      <c r="H31" s="50" t="inlineStr">
         <is>
           <t>Show placeholder greyed-out emotion bars so users know what to expect.</t>
         </is>
@@ -2535,41 +2624,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J31" s="39" t="inlineStr"/>
+      <c r="J31" s="47" t="inlineStr"/>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>H6-04</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="48" t="inlineStr">
         <is>
           <t>Recognition Rather Than Recall</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>Sidebar navigation</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>Navigation items use small pixel-art icons that are thematic but not universally recognisable. Labels compensate but icon meaning should be clearer.</t>
         </is>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="25" t="inlineStr">
+      <c r="H32" s="50" t="inlineStr">
         <is>
           <t>Add tooltip text on icon hover to reinforce meaning.</t>
         </is>
@@ -2579,41 +2668,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J32" s="39" t="inlineStr"/>
+      <c r="J32" s="47" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="48" t="inlineStr">
         <is>
           <t>H6-05</t>
         </is>
       </c>
-      <c r="B33" s="24" t="n">
+      <c r="B33" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="48" t="inlineStr">
         <is>
           <t>Recognition Rather Than Recall</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – text input</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>There is no example or suggestion of what kind of input produces interesting results.</t>
         </is>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="H33" s="50" t="inlineStr">
         <is>
           <t>Add 2–3 rotating example prompts or a hint below the input field.</t>
         </is>
@@ -2623,43 +2712,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J33" s="39" t="inlineStr"/>
+      <c r="J33" s="47" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>H7-01</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>All visualization pages – keyboard</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="46" t="inlineStr">
         <is>
           <t>Pressing Enter in the text field triggers analysis — a useful power-user shortcut.</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="G34" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H34" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -2669,43 +2758,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J34" s="39" t="inlineStr"/>
+      <c r="J34" s="47" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="44" t="inlineStr">
         <is>
           <t>H7-02</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>Settings – model selection</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="46" t="inlineStr">
         <is>
           <t>Expert users can select the large model for better accuracy. This two-tier design is good flexibility.</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="G35" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -2715,41 +2804,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J35" s="39" t="inlineStr"/>
+      <c r="J35" s="47" t="inlineStr"/>
     </row>
     <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="48" t="inlineStr">
         <is>
           <t>H7-03</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C36" s="48" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>There is no way to re-run analysis with the previous transcript without retyping it. No recent input history or Re-analyse button.</t>
         </is>
       </c>
-      <c r="G36" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="G36" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="50" t="inlineStr">
         <is>
           <t>Add a recent input history dropdown or a Re-analyse button.</t>
         </is>
@@ -2759,41 +2848,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J36" s="39" t="inlineStr"/>
+      <c r="J36" s="47" t="inlineStr"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="48" t="inlineStr">
         <is>
           <t>H7-04</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C37" s="48" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="48" t="inlineStr">
         <is>
           <t>Gallery page</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>There is no bulk action system — users must delete, rename, or favourite items one at a time.</t>
         </is>
       </c>
-      <c r="G37" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="G37" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="50" t="inlineStr">
         <is>
           <t>Add checkboxes for multi-select with bulk delete/download/favourite actions.</t>
         </is>
@@ -2803,41 +2892,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J37" s="39" t="inlineStr"/>
+      <c r="J37" s="47" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>H7-05</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
+      <c r="B38" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C38" s="48" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="48" t="inlineStr">
         <is>
           <t>Settings page</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>Settings are stored in localStorage only. Users who switch browsers or devices must reconfigure everything manually.</t>
         </is>
       </c>
-      <c r="G38" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="G38" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="50" t="inlineStr">
         <is>
           <t>Add Export Settings (download JSON) and Import Settings (upload JSON) buttons.</t>
         </is>
@@ -2847,41 +2936,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J38" s="39" t="inlineStr"/>
+      <c r="J38" s="47" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="48" t="inlineStr">
         <is>
           <t>H7-06</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n">
+      <c r="B39" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="48" t="inlineStr">
         <is>
           <t>Flexibility and Efficiency of Use</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="48" t="inlineStr">
         <is>
           <t>Anamorphic Resonance page</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>The WebGL shader has no user-adjustable parameters. Expert users have no way to fine-tune the visual output.</t>
         </is>
       </c>
-      <c r="G39" s="24" t="n">
+      <c r="G39" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="25" t="inlineStr">
+      <c r="H39" s="50" t="inlineStr">
         <is>
           <t>Consider exposing 1–2 sliders (e.g. complexity, speed) for advanced users.</t>
         </is>
@@ -2891,43 +2980,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J39" s="39" t="inlineStr"/>
+      <c r="J39" s="47" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="44" t="inlineStr">
         <is>
           <t>H8-01</t>
         </is>
       </c>
-      <c r="B40" s="18" t="n">
+      <c r="B40" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="44" t="inlineStr">
         <is>
           <t>Aesthetic and Minimalist Design</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>All pages – typography</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="46" t="inlineStr">
         <is>
           <t>The Press Start 2P pixel font is distinctive and thematically appropriate, reinforcing the retro-digital aesthetic.</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="G40" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="H40" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -2937,41 +3026,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J40" s="39" t="inlineStr"/>
+      <c r="J40" s="47" t="inlineStr"/>
     </row>
     <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="48" t="inlineStr">
         <is>
           <t>H8-02</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C41" s="48" t="inlineStr">
         <is>
           <t>Aesthetic and Minimalist Design</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – parameter readout</t>
         </is>
       </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F41" s="50" t="inlineStr">
         <is>
           <t>The f/k simulation parameter display is debug-level information that serves no purpose for most users and clutters the canvas overlay.</t>
         </is>
       </c>
-      <c r="G41" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="G41" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="50" t="inlineStr">
         <is>
           <t>Remove or hide behind a developer/debug toggle.</t>
         </is>
@@ -2981,41 +3070,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J41" s="39" t="inlineStr"/>
+      <c r="J41" s="47" t="inlineStr"/>
     </row>
     <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>H8-03</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
+      <c r="B42" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="C42" s="48" t="inlineStr">
         <is>
           <t>Aesthetic and Minimalist Design</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – overlay panel</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F42" s="50" t="inlineStr">
         <is>
           <t>The control dock overlays the visual stage, covering a significant portion of the artwork. On smaller viewports the panel can obscure most of the canvas.</t>
         </is>
       </c>
-      <c r="G42" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="G42" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="50" t="inlineStr">
         <is>
           <t>Make the overlay panel collapsible / minimisable with a toggle button.</t>
         </is>
@@ -3025,43 +3114,43 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J42" s="39" t="inlineStr"/>
+      <c r="J42" s="47" t="inlineStr"/>
     </row>
     <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="44" t="inlineStr">
         <is>
           <t>H8-04</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B43" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>Aesthetic and Minimalist Design</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>Gallery page – empty state</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F43" s="46" t="inlineStr">
         <is>
           <t>The empty state is minimal and sufficient. The design does not overload users with unnecessary options before they have artwork.</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="G43" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="H43" s="46" t="inlineStr">
         <is>
           <t>No action needed</t>
         </is>
@@ -3071,41 +3160,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J43" s="39" t="inlineStr"/>
+      <c r="J43" s="47" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="48" t="inlineStr">
         <is>
           <t>H8-05</t>
         </is>
       </c>
-      <c r="B44" s="24" t="n">
+      <c r="B44" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="48" t="inlineStr">
         <is>
           <t>Aesthetic and Minimalist Design</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="48" t="inlineStr">
         <is>
           <t>Settings page</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F44" s="25" t="inlineStr">
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F44" s="50" t="inlineStr">
         <is>
           <t>The settings page has six visually heavy card sections, causing significant scrolling on standard screens.</t>
         </is>
       </c>
-      <c r="G44" s="24" t="n">
+      <c r="G44" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="25" t="inlineStr">
+      <c r="H44" s="50" t="inlineStr">
         <is>
           <t>Consider grouping into tabs (Appearance, Input, Storage) to reduce page length.</t>
         </is>
@@ -3115,137 +3204,137 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J44" s="39" t="inlineStr"/>
+      <c r="J44" s="47" t="inlineStr"/>
     </row>
     <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>H9-01</t>
         </is>
       </c>
-      <c r="B45" s="27" t="n">
+      <c r="B45" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr">
         <is>
           <t>Help Users Recognize, Diagnose, and Recover from Errors</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – model error</t>
         </is>
       </c>
-      <c r="E45" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F45" s="28" t="inlineStr">
+      <c r="E45" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F45" s="57" t="inlineStr">
         <is>
           <t>When the emotion model returns a 503 error, the status shows "Model error" with raw technical text. The message does not explain what went wrong or what to do.</t>
         </is>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="28" t="inlineStr">
+      <c r="H45" s="57" t="inlineStr">
         <is>
           <t>Show a friendly message: "The emotion model isn’t ready yet. Try again in a moment, or switch to the Fast Model in Settings."</t>
         </is>
       </c>
-      <c r="I45" s="40" t="inlineStr">
+      <c r="I45" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J45" s="41" t="inlineStr">
+      <c r="J45" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t>H9-02</t>
         </is>
       </c>
-      <c r="B46" s="27" t="n">
+      <c r="B46" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C46" s="55" t="inlineStr">
         <is>
           <t>Help Users Recognize, Diagnose, and Recover from Errors</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – network error</t>
         </is>
       </c>
-      <c r="E46" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F46" s="28" t="inlineStr">
+      <c r="E46" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F46" s="57" t="inlineStr">
         <is>
           <t>Network fetch failures show a disruptive browser alert() with raw JavaScript error text that is not meaningful to users.</t>
         </is>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="H46" s="57" t="inlineStr">
         <is>
           <t>Replace alert() with inline error display in the status/output cells using friendly language.</t>
         </is>
       </c>
-      <c r="I46" s="40" t="inlineStr">
+      <c r="I46" s="54" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="J46" s="41" t="inlineStr">
+      <c r="J46" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="48" t="inlineStr">
         <is>
           <t>H9-03</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n">
+      <c r="B47" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="C47" s="48" t="inlineStr">
         <is>
           <t>Help Users Recognize, Diagnose, and Recover from Errors</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D47" s="48" t="inlineStr">
         <is>
           <t>Settings – model status</t>
         </is>
       </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F47" s="50" t="inlineStr">
         <is>
           <t>When the large model fails to download, the status shows "Error" with a technical detail string and no clear recovery path.</t>
         </is>
       </c>
-      <c r="G47" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="G47" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="50" t="inlineStr">
         <is>
           <t>Add a Retry Download button and suggest falling back to the base model.</t>
         </is>
@@ -3255,89 +3344,89 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J47" s="39" t="inlineStr"/>
+      <c r="J47" s="47" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>H9-04</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n">
+      <c r="B48" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="58" t="inlineStr">
         <is>
           <t>Help Users Recognize, Diagnose, and Recover from Errors</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="58" t="inlineStr">
         <is>
           <t>Gallery – file operations</t>
         </is>
       </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="E48" s="59" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>If a rename or delete API call fails, the error is shown via alert() with no retry mechanism or guidance.</t>
         </is>
       </c>
-      <c r="G48" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="22" t="inlineStr">
+      <c r="G48" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="60" t="inlineStr">
         <is>
           <t>Replace alert() with inline error in the card; add a retry button.</t>
         </is>
       </c>
-      <c r="I48" s="42" t="inlineStr">
+      <c r="I48" s="61" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="J48" s="43" t="inlineStr">
+      <c r="J48" s="47" t="inlineStr">
         <is>
           <t>19 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="48" t="inlineStr">
         <is>
           <t>H9-05</t>
         </is>
       </c>
-      <c r="B49" s="27" t="n">
+      <c r="B49" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C49" s="48" t="inlineStr">
         <is>
           <t>Help Users Recognize, Diagnose, and Recover from Errors</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – WebGL fallback</t>
         </is>
       </c>
-      <c r="E49" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F49" s="28" t="inlineStr">
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F49" s="50" t="inlineStr">
         <is>
           <t>The NEAREST filtering fallback happens silently. If even NEAREST fails, the page shows a completely black canvas with no explanation.</t>
         </is>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="28" t="inlineStr">
+      <c r="H49" s="50" t="inlineStr">
         <is>
           <t>Detect render failure explicitly and show: "Your browser’s graphics card does not support this visualisation. Try a different theme."</t>
         </is>
@@ -3347,41 +3436,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J49" s="39" t="inlineStr"/>
+      <c r="J49" s="47" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="48" t="inlineStr">
         <is>
           <t>H10-01</t>
         </is>
       </c>
-      <c r="B50" s="27" t="n">
+      <c r="B50" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="48" t="inlineStr">
         <is>
           <t>Help and Documentation</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="48" t="inlineStr">
         <is>
           <t>Whole application</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F50" s="28" t="inlineStr">
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F50" s="50" t="inlineStr">
         <is>
           <t>There is no help page, FAQ, user guide, or in-app documentation of any kind.</t>
         </is>
       </c>
-      <c r="G50" s="27" t="n">
+      <c r="G50" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="28" t="inlineStr">
+      <c r="H50" s="50" t="inlineStr">
         <is>
           <t>Add a minimal Help page covering: how to use the mic, what emotions are detected, how the gallery works, and how to switch themes.</t>
         </is>
@@ -3391,41 +3480,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J50" s="39" t="inlineStr"/>
+      <c r="J50" s="47" t="inlineStr"/>
     </row>
     <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="48" t="inlineStr">
         <is>
           <t>H10-02</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n">
+      <c r="B51" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="48" t="inlineStr">
         <is>
           <t>Help and Documentation</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="48" t="inlineStr">
         <is>
           <t>Home page – theme selection</t>
         </is>
       </c>
-      <c r="E51" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="E51" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F51" s="50" t="inlineStr">
         <is>
           <t>Theme cards show a title and one-line description but no indication of what user input is required or what to expect from the interaction.</t>
         </is>
       </c>
-      <c r="G51" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="G51" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="50" t="inlineStr">
         <is>
           <t>Add a brief How to use step list on the home page.</t>
         </is>
@@ -3435,41 +3524,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J51" s="39" t="inlineStr"/>
+      <c r="J51" s="47" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="48" t="inlineStr">
         <is>
           <t>H10-03</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n">
+      <c r="B52" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C52" s="48" t="inlineStr">
         <is>
           <t>Help and Documentation</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D52" s="48" t="inlineStr">
         <is>
           <t>Settings page – model selection</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F52" s="50" t="inlineStr">
         <is>
           <t>The difference between Fast Model and Large Model is not explained. Users cannot make an informed choice.</t>
         </is>
       </c>
-      <c r="G52" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
+      <c r="G52" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="50" t="inlineStr">
         <is>
           <t>Add a tooltip explaining: accuracy trade-off, download size, and load time for each model.</t>
         </is>
@@ -3479,41 +3568,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J52" s="39" t="inlineStr"/>
+      <c r="J52" s="47" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="48" t="inlineStr">
         <is>
           <t>H10-04</t>
         </is>
       </c>
-      <c r="B53" s="24" t="n">
+      <c r="B53" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="48" t="inlineStr">
         <is>
           <t>Help and Documentation</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="48" t="inlineStr">
         <is>
           <t>Settings page – Emotion Model card</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F53" s="25" t="inlineStr">
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
         <is>
           <t>The model status messages (Idle, Loading, Ready) lack context about what they mean or how long loading will take.</t>
         </is>
       </c>
-      <c r="G53" s="24" t="n">
+      <c r="G53" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="25" t="inlineStr">
+      <c r="H53" s="50" t="inlineStr">
         <is>
           <t>Add a sub-label under each status e.g. "Ready – large model loaded and available for use."</t>
         </is>
@@ -3523,41 +3612,41 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J53" s="39" t="inlineStr"/>
+      <c r="J53" s="47" t="inlineStr"/>
     </row>
     <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="48" t="inlineStr">
         <is>
           <t>H10-05</t>
         </is>
       </c>
-      <c r="B54" s="21" t="n">
+      <c r="B54" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C54" s="48" t="inlineStr">
         <is>
           <t>Help and Documentation</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="48" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="F54" s="50" t="inlineStr">
         <is>
           <t>First-time users have no onboarding. The interface launches directly into the art visualisation with no explanation of how to interact with it.</t>
         </is>
       </c>
-      <c r="G54" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="22" t="inlineStr">
+      <c r="G54" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="50" t="inlineStr">
         <is>
           <t>Add a one-time dismissible tooltip overlay on first visit guiding users through the basic workflow.</t>
         </is>
@@ -3567,7 +3656,7 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="J54" s="39" t="inlineStr"/>
+      <c r="J54" s="47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3580,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3589,6 +3678,7 @@
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3597,1268 +3687,1498 @@
           <t>Issues Ranked by Severity</t>
         </is>
       </c>
+      <c r="G1" s="37" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="62" t="inlineStr">
         <is>
           <t>H#</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="62" t="inlineStr">
         <is>
           <t>Page / Location</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="62" t="inlineStr">
         <is>
           <t>Issue Description</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="62" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
+      <c r="G2" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="52" t="inlineStr">
         <is>
           <t>H3-03</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="51" t="inlineStr">
         <is>
           <t>Settings – Clear Gallery</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>Clear Gallery deletes all artwork permanently with only a browser confirm(). No undo, no export prompt, no recovery.</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
         <is>
           <t>Require typed confirmation (type DELETE) and offer Download all first option.</t>
         </is>
       </c>
+      <c r="G3" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>H5-02</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Settings – Clear Gallery</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>A single browser confirm() dialog is the only barrier before all gallery data is permanently deleted.</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="53" t="inlineStr">
         <is>
           <t>Require the user to type DELETE or tick a checkbox to confirm intent.</t>
         </is>
       </c>
+      <c r="G4" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>H3-01</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – mic input</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="50" t="inlineStr">
         <is>
           <t>No way to cancel speech recognition without triggering full analysis. No discard option.</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>Add a Discard action that stops the mic without triggering analysis.</t>
         </is>
       </c>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>H3-02</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Gallery – delete action</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="50" t="inlineStr">
         <is>
           <t>Delete action uses browser confirm() with no undo. Deletion is permanent.</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>Implement short-lived undo toast or trash system.</t>
         </is>
       </c>
+      <c r="G6" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>H5-03</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>Settings – filename pattern</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="57" t="inlineStr">
         <is>
           <t>No validation for filename pattern; illegal characters cause silent save failures.</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="57" t="inlineStr">
         <is>
           <t>Validate pattern in real time; show error for illegal characters.</t>
         </is>
       </c>
+      <c r="G7" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>H5-05</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – mic button</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="57" t="inlineStr">
         <is>
           <t>Permission denied shows "Mic error" without explaining how to grant permission.</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="57" t="inlineStr">
         <is>
           <t>Detect permission denied and show guidance linking to browser mic settings.</t>
         </is>
       </c>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>H9-01</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – model error</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="57" t="inlineStr">
         <is>
           <t>503 error shows raw technical "Model error" text with no explanation or recovery path.</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="57" t="inlineStr">
         <is>
           <t>Show friendly message directing user to Settings to switch model.</t>
         </is>
       </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
         <is>
           <t>H9-02</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>All visualization pages – network error</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="57" t="inlineStr">
         <is>
           <t>Network failures show disruptive browser alert() with raw JavaScript error text.</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="57" t="inlineStr">
         <is>
           <t>Replace alert() with inline error display using friendly language.</t>
         </is>
       </c>
+      <c r="G10" s="54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>H9-05</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – WebGL fallback</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="50" t="inlineStr">
         <is>
           <t>If even NEAREST fallback fails, canvas shows completely black with no explanation.</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>Detect render failure and show: "Your browser does not support this visualisation. Try a different theme."</t>
         </is>
       </c>
+      <c r="G11" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>H10-01</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>Whole application</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="50" t="inlineStr">
         <is>
           <t>No help page, FAQ, user guide, or in-app documentation of any kind.</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>Add minimal Help page covering mic use, emotion detection, gallery, and theme switching.</t>
         </is>
       </c>
+      <c r="G12" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="A13" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>H1-03</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – Save button</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="50" t="inlineStr">
         <is>
           <t>Save feedback shows SAVED for only 1.2 seconds; easy to miss.</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>Extend to 3 seconds; add persistent toast.</t>
         </is>
       </c>
+      <c r="G13" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="A14" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>H1-04</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – canvas</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="50" t="inlineStr">
         <is>
           <t>No indication simulation is running vs. frozen.</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>Add animated pulse or LIVE badge.</t>
         </is>
       </c>
+      <c r="G14" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="A15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>H1-05</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Home page – theme cards</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="50" t="inlineStr">
         <is>
           <t>Static thumbnails give no preview of dynamic art.</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>Add looping GIF or video previews on hover.</t>
         </is>
       </c>
+      <c r="G15" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="A16" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>H2-01</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="C16" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Home page – theme descriptions</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="50" t="inlineStr">
         <is>
           <t>Technical names unfamiliar to general users.</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>Add plain-English sub-descriptions.</t>
         </is>
       </c>
+      <c r="G16" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="A17" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>H2-04</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="C17" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Settings page – Filename Pattern</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="50" t="inlineStr">
         <is>
           <t>Template tokens not explained; users may not understand the substitution syntax.</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>Add live preview or tooltip explaining tokens.</t>
         </is>
       </c>
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="A18" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>H3-04</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – theme switching</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>Switching theme requires returning to home, losing analysis state.</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>Add theme-switcher dropdown in page header.</t>
         </is>
       </c>
+      <c r="G18" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="A19" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>H3-05</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – canvas reset</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="50" t="inlineStr">
         <is>
           <t>No reset button; if pattern converges users are stuck.</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>Add Reset button to reinitialise simulation.</t>
         </is>
       </c>
+      <c r="G19" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="A20" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>H4-02</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Home page vs. visualization pages</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="50" t="inlineStr">
         <is>
           <t>Sidebar absent on home page; layout discontinuity.</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>Apply full app-shell to home page.</t>
         </is>
       </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="A21" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>H4-04</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Settings page – button placement</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="50" t="inlineStr">
         <is>
           <t>Save/Restore buttons at bottom of long page with no sticky bar.</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>Make save footer sticky or add top duplicate.</t>
         </is>
       </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="A22" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>H4-06</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Gallery View page</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="50" t="inlineStr">
         <is>
           <t>Fullscreen view lacks Rename and Favourite actions present on gallery grid.</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>Add Rename and Favourite to gallery_view page.</t>
         </is>
       </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="A23" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>H5-01</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – Generate button</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="50" t="inlineStr">
         <is>
           <t>Empty text submission silently ignored with no feedback.</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>Disable Generate when empty or show inline message.</t>
         </is>
       </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="A24" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>H5-04</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Bubbles page</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="50" t="inlineStr">
         <is>
           <t>No user-facing error if WebGL fallback fails.</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="50" t="inlineStr">
         <is>
           <t>Add error banner if simulation cannot render.</t>
         </is>
       </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="A25" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>H7-03</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="50" t="inlineStr">
         <is>
           <t>No way to re-run previous analysis without retyping.</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>Add recent input history dropdown or Re-analyse button.</t>
         </is>
       </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="A26" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>H7-04</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>Gallery page</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="50" t="inlineStr">
         <is>
           <t>No bulk actions; users must manage items one at a time.</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="50" t="inlineStr">
         <is>
           <t>Add multi-select with bulk delete/download/favourite.</t>
         </is>
       </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="A27" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>H7-05</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Settings page</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="50" t="inlineStr">
         <is>
           <t>Settings stored in localStorage only; lost on device/browser change.</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>Add Export Settings and Import Settings (JSON).</t>
         </is>
       </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="A28" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>H8-02</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – parameter readout</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="50" t="inlineStr">
         <is>
           <t>f/k parameter display is debug-level, meaningless to users.</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="50" t="inlineStr">
         <is>
           <t>Remove or hide behind debug toggle.</t>
         </is>
       </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="A29" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>H8-03</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – overlay panel</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="50" t="inlineStr">
         <is>
           <t>Control dock covers significant portion of artwork; worse on small screens.</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="50" t="inlineStr">
         <is>
           <t>Make overlay panel collapsible.</t>
         </is>
       </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="A30" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>H9-03</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>Settings – model status</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="50" t="inlineStr">
         <is>
           <t>Large model failure shows technical error with no recovery path.</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="50" t="inlineStr">
         <is>
           <t>Add Retry Download button and suggest base model fallback.</t>
         </is>
       </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="A31" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>H9-04</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="58" t="inlineStr">
         <is>
           <t>Gallery – file operations</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="60" t="inlineStr">
         <is>
           <t>API failures shown via alert() with no retry.</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
         <is>
           <t>Replace alert() with inline card error and retry button.</t>
         </is>
       </c>
+      <c r="G31" s="61" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="A32" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>H10-02</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>Home page – theme selection</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="50" t="inlineStr">
         <is>
           <t>No how-to-use guidance on theme cards.</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>Add brief step list: 1. Choose theme 2. Type or speak 3. Watch the art.</t>
         </is>
       </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="A33" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>H10-03</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>Settings page – model selection</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="50" t="inlineStr">
         <is>
           <t>No explanation of difference between Fast and Large models.</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>Add tooltip explaining accuracy, size, and load time trade-offs.</t>
         </is>
       </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="A34" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>H10-05</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>All visualization pages</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="50" t="inlineStr">
         <is>
           <t>No first-time user onboarding.</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>Add dismissible tooltip overlay on first visit.</t>
         </is>
       </c>
+      <c r="G34" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="A35" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>H2-04</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="C35" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
         <is>
           <t>Settings – Filename Pattern</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="50" t="inlineStr">
         <is>
           <t>Template syntax not explained to users.</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="50" t="inlineStr">
         <is>
           <t>Add live filename preview or token explanation tooltip.</t>
         </is>
       </c>
+      <c r="G35" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="24" t="n">
+      <c r="A36" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>H1-06</t>
         </is>
       </c>
-      <c r="C36" s="24" t="n">
+      <c r="C36" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>Gallery page</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="50" t="inlineStr">
         <is>
           <t>No progress indicator for delete/favourite actions.</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>Add brief loading state to action buttons.</t>
         </is>
       </c>
+      <c r="G36" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="24" t="n">
+      <c r="A37" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>H2-02</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="C37" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="48" t="inlineStr">
         <is>
           <t>Bubbles page – parameter readout</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="50" t="inlineStr">
         <is>
           <t>Chemistry constants shown to non-specialist users.</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>Replace with emotion label or hide the readout.</t>
         </is>
       </c>
+      <c r="G37" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="24" t="n">
+      <c r="A38" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>H2-05</t>
         </is>
       </c>
-      <c r="C38" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="C38" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="48" t="inlineStr">
         <is>
           <t>Gallery page – card metadata</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="50" t="inlineStr">
         <is>
           <t>Route slug shown instead of display name.</t>
         </is>
       </c>
-      <c r="F38" s="25" t="inlineStr">
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>Map slugs to friendly names.</t>
         </is>
       </c>
+      <c r="G38" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="24" t="n">
+      <c r="A39" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>H4-03</t>
         </is>
       </c>
-      <c r="C39" s="24" t="n">
+      <c r="C39" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="48" t="inlineStr">
         <is>
           <t>Favourites page</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="50" t="inlineStr">
         <is>
           <t>No empty-state action button linking back to themes.</t>
         </is>
       </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>Add Browse Themes CTA in empty state.</t>
         </is>
       </c>
+      <c r="G39" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="24" t="n">
+      <c r="A40" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>H4-05</t>
         </is>
       </c>
-      <c r="C40" s="24" t="n">
+      <c r="C40" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="48" t="inlineStr">
         <is>
           <t>Sidebar – active state</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="50" t="inlineStr">
         <is>
           <t>Active state uses Jinja2 flags; risk of missing on new pages.</t>
         </is>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F40" s="50" t="inlineStr">
         <is>
           <t>Drive from current URL via JavaScript.</t>
         </is>
       </c>
+      <c r="G40" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="24" t="n">
+      <c r="A41" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="49" t="inlineStr">
         <is>
           <t>H6-03</t>
         </is>
       </c>
-      <c r="C41" s="24" t="n">
+      <c r="C41" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – emotion scores</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="50" t="inlineStr">
         <is>
           <t>No placeholder showing what analysis output looks like before first use.</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F41" s="50" t="inlineStr">
         <is>
           <t>Show greyed-out placeholder emotion bars.</t>
         </is>
       </c>
+      <c r="G41" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="24" t="n">
+      <c r="A42" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>H6-04</t>
         </is>
       </c>
-      <c r="C42" s="24" t="n">
+      <c r="C42" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>Sidebar navigation</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="50" t="inlineStr">
         <is>
           <t>Pixel-art icons not universally recognisable without labels.</t>
         </is>
       </c>
-      <c r="F42" s="25" t="inlineStr">
+      <c r="F42" s="50" t="inlineStr">
         <is>
           <t>Add hover tooltips to icon labels.</t>
         </is>
       </c>
+      <c r="G42" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="24" t="n">
+      <c r="A43" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>H6-05</t>
         </is>
       </c>
-      <c r="C43" s="24" t="n">
+      <c r="C43" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="48" t="inlineStr">
         <is>
           <t>All visualization pages – text input</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E43" s="50" t="inlineStr">
         <is>
           <t>No example prompts or hints about what input produces interesting results.</t>
         </is>
       </c>
-      <c r="F43" s="25" t="inlineStr">
+      <c r="F43" s="50" t="inlineStr">
         <is>
           <t>Add 2–3 rotating example prompts below input.</t>
         </is>
       </c>
+      <c r="G43" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="24" t="n">
+      <c r="A44" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>H7-06</t>
         </is>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C44" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="48" t="inlineStr">
         <is>
           <t>Anamorphic Resonance page</t>
         </is>
       </c>
-      <c r="E44" s="25" t="inlineStr">
+      <c r="E44" s="50" t="inlineStr">
         <is>
           <t>No user-adjustable parameters for expert customisation.</t>
         </is>
       </c>
-      <c r="F44" s="25" t="inlineStr">
+      <c r="F44" s="50" t="inlineStr">
         <is>
           <t>Consider 1–2 sliders (complexity, speed) for advanced users.</t>
         </is>
       </c>
+      <c r="G44" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="24" t="n">
+      <c r="A45" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>H8-05</t>
         </is>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="48" t="inlineStr">
         <is>
           <t>Settings page</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E45" s="50" t="inlineStr">
         <is>
           <t>Six heavy card sections cause significant scrolling.</t>
         </is>
       </c>
-      <c r="F45" s="25" t="inlineStr">
+      <c r="F45" s="50" t="inlineStr">
         <is>
           <t>Group into tabs (Appearance, Input, Storage).</t>
         </is>
       </c>
+      <c r="G45" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="24" t="n">
+      <c r="A46" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>H10-04</t>
         </is>
       </c>
-      <c r="C46" s="24" t="n">
+      <c r="C46" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="48" t="inlineStr">
         <is>
           <t>Settings – Emotion Model card</t>
         </is>
       </c>
-      <c r="E46" s="25" t="inlineStr">
+      <c r="E46" s="50" t="inlineStr">
         <is>
           <t>Status messages lack explanatory context.</t>
         </is>
       </c>
-      <c r="F46" s="25" t="inlineStr">
+      <c r="F46" s="50" t="inlineStr">
         <is>
           <t>Add sub-label explaining each status state.</t>
+        </is>
+      </c>
+      <c r="G46" s="63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4895,32 +5215,32 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="62" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="62" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="62" t="inlineStr">
         <is>
           <t>H#</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="62" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -4934,112 +5254,112 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>All Pages / Global</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>H10-01</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D4" s="27" t="n">
+      <c r="C4" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D4" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>No help page, FAQ, or in-app documentation of any kind.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>All Pages / Global</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>H7-01</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>Enter key in text field triggers analysis — useful keyboard shortcut.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>All Pages / Global</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>H4-01</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="46" t="inlineStr">
         <is>
           <t>All five visualization pages share the same control dock layout — excellent consistency.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>All Pages / Global</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>H8-01</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="46" t="inlineStr">
         <is>
           <t>Press Start 2P pixel font reinforces the retro-digital aesthetic effectively.</t>
         </is>
@@ -5053,112 +5373,112 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>Home Page (/)</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>H1-05</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>Static theme thumbnails give no preview of the dynamic art.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>Home Page (/)</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>H2-01</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>Technical theme names (e.g. Anamorphic Resonance) unfamiliar to general users.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>Home Page (/)</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>H4-02</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="21" t="n">
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>Sidebar absent on home page — layout discontinuity vs all other pages.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Home Page (/)</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>H10-02</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="21" t="n">
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D12" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>No how-to-use guidance on theme selection page.</t>
         </is>
@@ -5172,392 +5492,392 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="45" t="inlineStr">
         <is>
           <t>H1-01</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="46" t="inlineStr">
         <is>
           <t>Status readout transitions clearly through Ready → Listening → Analysing → Ready.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>H1-03</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="21" t="n">
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>Save feedback shows SAVED for only 1.2 seconds; easy to miss.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="45" t="inlineStr">
         <is>
           <t>H2-03</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="E16" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
         <is>
           <t>START LISTENING / END LISTENING labels match common voice interface conventions.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>H3-01</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="n">
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>No way to cancel speech recognition without triggering full analysis.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>H3-04</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="21" t="n">
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>Switching theme requires returning to home, abandoning current session.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>H5-01</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="21" t="n">
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>Empty text submission silently ignored with no user feedback.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="56" t="inlineStr">
         <is>
           <t>H5-05</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="n">
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="57" t="inlineStr">
         <is>
           <t>Mic permission denied shows "Mic error" without guidance on how to fix it.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>H6-03</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="n">
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>No placeholder showing what analysis output looks like before first use.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>H6-05</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="n">
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>No example prompts or hints about what input produces interesting results.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>H7-03</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="21" t="n">
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>No way to re-run previous analysis without retyping the input.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>H8-03</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="21" t="n">
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="50" t="inlineStr">
         <is>
           <t>Control dock overlays and covers significant portion of the visual artwork.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>H9-01</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="n">
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="57" t="inlineStr">
         <is>
           <t>Model error shows raw technical text with no explanation or recovery path.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>H9-02</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D26" s="27" t="n">
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="57" t="inlineStr">
         <is>
           <t>Network failures show disruptive browser alert() with raw error text.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>All Visualization Pages</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>H10-05</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="21" t="n">
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>No first-time user onboarding or guided introduction.</t>
         </is>
@@ -5571,28 +5891,28 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="48" t="inlineStr">
         <is>
           <t>Anamorphic Resonance</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>H7-06</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="n">
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="50" t="inlineStr">
         <is>
           <t>No user-adjustable parameters for expert customisation of the shader.</t>
         </is>
@@ -5606,168 +5926,168 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>H1-04</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="21" t="n">
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="50" t="inlineStr">
         <is>
           <t>No indication whether the simulation is actively running or frozen.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>H2-02</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="n">
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="E32" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>f/k chemistry constants shown in canvas overlay; meaningless to users.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>H3-05</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="21" t="n">
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>No reset button; if pattern converges to uninteresting state users are stuck.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>H5-04</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="21" t="n">
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>No user-facing error if WebGL rendering fails after fallback attempts.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>H8-02</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="21" t="n">
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="50" t="inlineStr">
         <is>
           <t>f/k parameter readout is debug-level clutter on the canvas overlay.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="48" t="inlineStr">
         <is>
           <t>Bubbles (Reaction-Diffusion)</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>H9-05</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D36" s="27" t="n">
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>Black canvas on WebGL fallback failure with no explanation shown to user.</t>
         </is>
@@ -5781,196 +6101,196 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>H1-06</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="n">
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="25" t="inlineStr">
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>No progress indicator for delete or favourite actions.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="48" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>H2-05</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="n">
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="E39" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>Route slug shown instead of friendly display name on artwork cards.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="48" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>H3-02</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D40" s="27" t="n">
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="28" t="inlineStr">
+      <c r="F40" s="50" t="inlineStr">
         <is>
           <t>Delete is permanent with only a browser confirm(); no undo available.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="44" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="45" t="inlineStr">
         <is>
           <t>H6-01</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F41" s="46" t="inlineStr">
         <is>
           <t>Artwork cards show page source and thumbnail — supports visual recognition.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>H7-04</t>
         </is>
       </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="21" t="n">
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="50" t="inlineStr">
         <is>
           <t>No bulk actions; users must manage each item individually.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="44" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="45" t="inlineStr">
         <is>
           <t>H8-04</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F43" s="46" t="inlineStr">
         <is>
           <t>Empty state is minimal and clean — does not overload users with options.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>Gallery</t>
         </is>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>H9-04</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="21" t="n">
+      <c r="C44" s="59" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D44" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="60" t="inlineStr">
         <is>
           <t>API failures shown via alert() with no retry mechanism.</t>
         </is>
@@ -5984,28 +6304,28 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="48" t="inlineStr">
         <is>
           <t>Favourites</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>H4-03</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="n">
+      <c r="C46" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="24" t="n">
+      <c r="E46" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="25" t="inlineStr">
+      <c r="F46" s="50" t="inlineStr">
         <is>
           <t>No empty-state action button linking back to themes.</t>
         </is>
@@ -6019,28 +6339,28 @@
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="48" t="inlineStr">
         <is>
           <t>Gallery View (Fullscreen)</t>
         </is>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="49" t="inlineStr">
         <is>
           <t>H4-06</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" s="21" t="n">
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="50" t="inlineStr">
         <is>
           <t>Fullscreen view lacks Rename and Favourite actions present on gallery grid.</t>
         </is>
@@ -6054,364 +6374,364 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="44" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="45" t="inlineStr">
         <is>
           <t>H1-02</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D50" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F50" s="46" t="inlineStr">
         <is>
           <t>Model status panel polls every 3 seconds and shows clear state with spinner.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="49" t="inlineStr">
         <is>
           <t>H2-04</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="C51" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="50" t="inlineStr">
         <is>
           <t>Filename template tokens not explained; live preview absent.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="51" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="52" t="inlineStr">
         <is>
           <t>H3-03</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
+      <c r="C52" s="52" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D52" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="E52" s="30" t="n">
+      <c r="E52" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="31" t="inlineStr">
+      <c r="F52" s="53" t="inlineStr">
         <is>
           <t>Clear Gallery deletes all artwork permanently with only a confirm() dialog.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B53" s="49" t="inlineStr">
         <is>
           <t>H4-04</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="21" t="n">
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="50" t="inlineStr">
         <is>
           <t>Save/Restore buttons at bottom of long page with no sticky footer.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="51" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="52" t="inlineStr">
         <is>
           <t>H5-02</t>
         </is>
       </c>
-      <c r="C54" s="30" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D54" s="30" t="n">
+      <c r="C54" s="52" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D54" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="E54" s="30" t="n">
+      <c r="E54" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="F54" s="31" t="inlineStr">
+      <c r="F54" s="53" t="inlineStr">
         <is>
           <t>Single browser confirm() is the only barrier to permanently deleting all gallery data.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="55" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B55" s="27" t="inlineStr">
+      <c r="B55" s="56" t="inlineStr">
         <is>
           <t>H5-03</t>
         </is>
       </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D55" s="27" t="n">
+      <c r="C55" s="56" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D55" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="27" t="n">
+      <c r="E55" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="F55" s="28" t="inlineStr">
+      <c r="F55" s="57" t="inlineStr">
         <is>
           <t>No validation of filename pattern; illegal characters cause silent failures.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="45" t="inlineStr">
         <is>
           <t>H6-02</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="D56" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E56" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F56" s="46" t="inlineStr">
         <is>
           <t>All settings use dropdowns and checkboxes — recognition over recall.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="45" t="inlineStr">
         <is>
           <t>H7-02</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="45" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D57" s="18" t="n">
+      <c r="D57" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="18" t="n">
+      <c r="E57" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F57" s="46" t="inlineStr">
         <is>
           <t>Two-tier model selection supports expert users who need higher accuracy.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="B58" s="49" t="inlineStr">
         <is>
           <t>H7-05</t>
         </is>
       </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" s="21" t="n">
+      <c r="C58" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D58" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="50" t="inlineStr">
         <is>
           <t>Settings in localStorage only; lost when switching browser or device.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B59" s="49" t="inlineStr">
         <is>
           <t>H8-05</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="n">
+      <c r="C59" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="24" t="n">
+      <c r="E59" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="25" t="inlineStr">
+      <c r="F59" s="50" t="inlineStr">
         <is>
           <t>Six heavy card sections cause significant scrolling on standard screens.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B60" s="21" t="inlineStr">
+      <c r="B60" s="49" t="inlineStr">
         <is>
           <t>H9-03</t>
         </is>
       </c>
-      <c r="C60" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="21" t="n">
+      <c r="C60" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D60" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="F60" s="22" t="inlineStr">
+      <c r="F60" s="50" t="inlineStr">
         <is>
           <t>Large model failure shows technical error string with no clear recovery path.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B61" s="49" t="inlineStr">
         <is>
           <t>H10-03</t>
         </is>
       </c>
-      <c r="C61" s="21" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="21" t="n">
+      <c r="C61" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D61" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F61" s="50" t="inlineStr">
         <is>
           <t>No explanation of Fast vs Large model difference or trade-offs.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="23" t="inlineStr">
+      <c r="A62" s="48" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B62" s="49" t="inlineStr">
         <is>
           <t>H10-04</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="n">
+      <c r="C62" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="24" t="n">
+      <c r="E62" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="F62" s="25" t="inlineStr">
+      <c r="F62" s="50" t="inlineStr">
         <is>
           <t>Model status messages lack explanatory context or time estimates.</t>
         </is>
@@ -6425,56 +6745,56 @@
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="48" t="inlineStr">
         <is>
           <t>Sidebar / Navigation</t>
         </is>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="49" t="inlineStr">
         <is>
           <t>H4-05</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="n">
+      <c r="C64" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D64" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="24" t="n">
+      <c r="E64" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="25" t="inlineStr">
+      <c r="F64" s="50" t="inlineStr">
         <is>
           <t>Active state uses Jinja2 template flags; risk of missing on new pages.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A65" s="48" t="inlineStr">
         <is>
           <t>Sidebar / Navigation</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B65" s="49" t="inlineStr">
         <is>
           <t>H6-04</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="n">
+      <c r="C65" s="49" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+      <c r="D65" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="24" t="n">
+      <c r="E65" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="F65" s="25" t="inlineStr">
+      <c r="F65" s="50" t="inlineStr">
         <is>
           <t>Pixel-art navigation icons not universally recognisable without labels.</t>
         </is>
